--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$60</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -437,33 +437,220 @@
     <t>Condition.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Condition.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Auteur du problème</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.id</t>
+  </si>
+  <si>
+    <t>Condition.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:actor.id</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:actor.url</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
+</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.url</t>
+  </si>
+  <si>
+    <t>Condition.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Condition.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Condition.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -471,6 +658,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -508,10 +698,6 @@
     <t>Condition.clinicalStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Statut du problème</t>
   </si>
   <si>
@@ -519,9 +705,6 @@
   </si>
   <si>
     <t>The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>The clinical status of the condition or diagnosis.</t>
@@ -805,9 +988,6 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Event.occurrence[x]</t>
   </si>
   <si>
@@ -901,274 +1081,6 @@
     <t>FiveWs.author</t>
   </si>
   <si>
-    <t>Condition.recorder.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
-</t>
-  </si>
-  <si>
-    <t>Auteur du problème</t>
-  </si>
-  <si>
-    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.id</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:type.id</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:type.url</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:typeCode</t>
-  </si>
-  <si>
-    <t>typeCode</t>
-  </si>
-  <si>
-    <t>Type de participation</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:actor</t>
-  </si>
-  <si>
-    <t>actor</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:actor.id</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:actor.url</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
-</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.url</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension:author.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.recorder.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Condition.recorder.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>Condition.recorder.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>Condition.recorder.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>Condition.recorder.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
-  </si>
-  <si>
     <t>Condition.asserter</t>
   </si>
   <si>
@@ -1211,6 +1123,12 @@
   </si>
   <si>
     <t>Condition.stage.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Condition.stage.modifierExtension</t>
@@ -1688,11 +1606,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP66"/>
+  <dimension ref="A1:AP60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.93359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.16015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.73828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.96484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.1640625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2707,7 +2625,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2726,17 +2644,15 @@
         <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>79</v>
@@ -2773,16 +2689,14 @@
         <v>79</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -2809,7 +2723,7 @@
         <v>79</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>79</v>
@@ -2823,43 +2737,41 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>79</v>
       </c>
@@ -2907,7 +2819,7 @@
         <v>79</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2916,7 +2828,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>79</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -2931,7 +2843,7 @@
         <v>79</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>79</v>
@@ -2940,12 +2852,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2953,35 +2865,31 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O11" t="s" s="2">
         <v>153</v>
       </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>79</v>
       </c>
@@ -3029,22 +2937,22 @@
         <v>79</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>79</v>
@@ -3056,15 +2964,15 @@
         <v>155</v>
       </c>
       <c r="AO11" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP11" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" hidden="true">
+      <c r="A12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>157</v>
@@ -3075,32 +2983,30 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>79</v>
@@ -3125,102 +3031,102 @@
         <v>79</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP12" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
+      <c r="A13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="Y12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>79</v>
@@ -3245,13 +3151,13 @@
         <v>79</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>175</v>
+        <v>79</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>79</v>
@@ -3269,45 +3175,45 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>170</v>
+        <v>79</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3315,13 +3221,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>79</v>
@@ -3330,17 +3236,15 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>79</v>
@@ -3365,11 +3269,13 @@
         <v>79</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>79</v>
@@ -3387,45 +3293,45 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>79</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3436,10 +3342,10 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>79</v>
@@ -3448,17 +3354,15 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>79</v>
@@ -3483,71 +3387,73 @@
         <v>79</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>196</v>
+        <v>79</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>79</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3557,33 +3463,33 @@
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>79</v>
@@ -3601,13 +3507,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3625,10 +3531,10 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>91</v>
@@ -3637,33 +3543,33 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>214</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3674,29 +3580,27 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>79</v>
@@ -3706,7 +3610,7 @@
         <v>79</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>79</v>
@@ -3721,11 +3625,11 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3743,13 +3647,13 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>215</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>79</v>
@@ -3761,61 +3665,61 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>222</v>
+        <v>134</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>223</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
-      <c r="O18" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
@@ -3863,34 +3767,34 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>231</v>
+        <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>232</v>
+        <v>79</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -3898,10 +3802,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>234</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3921,20 +3825,18 @@
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>235</v>
+        <v>151</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>236</v>
+        <v>152</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3983,7 +3885,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>154</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3995,22 +3897,22 @@
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>241</v>
+        <v>155</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -4018,10 +3920,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>243</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>243</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4029,32 +3931,30 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>244</v>
+        <v>136</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>245</v>
+        <v>137</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>247</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4091,44 +3991,46 @@
         <v>79</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>249</v>
+        <v>140</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>160</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>252</v>
+        <v>79</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4136,20 +4038,18 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>254</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4161,19 +4061,19 @@
         <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>256</v>
+        <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>257</v>
+        <v>169</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>246</v>
+        <v>170</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>247</v>
+        <v>171</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4181,7 +4081,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>79</v>
@@ -4223,10 +4123,10 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>172</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>91</v>
@@ -4235,22 +4135,22 @@
         <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>252</v>
+        <v>134</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -4258,10 +4158,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>258</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>258</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4275,7 +4175,7 @@
         <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>79</v>
@@ -4284,17 +4184,15 @@
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4331,17 +4229,19 @@
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4350,7 +4250,7 @@
         <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>103</v>
@@ -4365,37 +4265,37 @@
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>258</v>
+        <v>157</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
@@ -4404,17 +4304,15 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>256</v>
+        <v>136</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>267</v>
+        <v>137</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
@@ -4463,19 +4361,19 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>258</v>
+        <v>160</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
@@ -4487,10 +4385,10 @@
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -4498,10 +4396,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>191</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>268</v>
+        <v>164</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4521,16 +4419,16 @@
         <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>256</v>
+        <v>151</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>270</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4581,7 +4479,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>268</v>
+        <v>154</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4593,7 +4491,7 @@
         <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>79</v>
@@ -4602,24 +4500,24 @@
         <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>271</v>
+        <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>272</v>
+        <v>155</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>274</v>
+        <v>192</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>274</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4630,25 +4528,25 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>137</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>138</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4687,31 +4585,31 @@
         <v>79</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>79</v>
+        <v>159</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>274</v>
+        <v>160</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
@@ -4723,10 +4621,10 @@
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>79</v>
@@ -4734,10 +4632,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>280</v>
+        <v>193</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>280</v>
+        <v>168</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4745,7 +4643,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>91</v>
@@ -4760,22 +4658,24 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>281</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>282</v>
+        <v>169</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>79</v>
@@ -4817,10 +4717,10 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>172</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>91</v>
@@ -4841,7 +4741,7 @@
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4852,21 +4752,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>286</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>79</v>
@@ -4878,17 +4778,15 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -4925,31 +4823,31 @@
         <v>79</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>290</v>
+        <v>180</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>79</v>
@@ -4961,7 +4859,7 @@
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -4972,20 +4870,18 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>196</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -5000,22 +4896,24 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>293</v>
+        <v>105</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>294</v>
+        <v>169</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>79</v>
@@ -5057,19 +4955,19 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>172</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>79</v>
@@ -5081,7 +4979,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5092,10 +4990,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>296</v>
+        <v>199</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5106,7 +5004,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>79</v>
@@ -5118,13 +5016,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>281</v>
+        <v>201</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>282</v>
+        <v>175</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5175,7 +5073,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5187,7 +5085,7 @@
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>79</v>
@@ -5199,7 +5097,7 @@
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>285</v>
+        <v>134</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5210,18 +5108,18 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>202</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>81</v>
@@ -5230,22 +5128,26 @@
         <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>301</v>
+        <v>204</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5281,19 +5183,19 @@
         <v>79</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>208</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5317,7 +5219,7 @@
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5328,23 +5230,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5353,19 +5253,23 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>211</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5413,7 +5317,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5425,10 +5329,10 @@
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>79</v>
+        <v>215</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>79</v>
@@ -5437,21 +5341,21 @@
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>79</v>
+        <v>216</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>218</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5459,30 +5363,32 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>281</v>
+        <v>188</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>219</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5507,13 +5413,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5531,7 +5437,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>284</v>
+        <v>218</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5540,36 +5446,36 @@
         <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>285</v>
+        <v>228</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5580,27 +5486,29 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>301</v>
+        <v>231</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5625,69 +5533,69 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>79</v>
+        <v>178</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>225</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>79</v>
+        <v>239</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>241</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5701,7 +5609,7 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
@@ -5710,16 +5618,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>311</v>
+        <v>242</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>313</v>
+        <v>244</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5727,7 +5635,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>304</v>
+        <v>79</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>79</v>
@@ -5745,13 +5653,11 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>79</v>
+        <v>245</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -5769,45 +5675,45 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>314</v>
+        <v>241</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>134</v>
+        <v>248</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>79</v>
+        <v>249</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>250</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>250</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5821,7 +5727,7 @@
         <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -5830,15 +5736,17 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -5848,7 +5756,7 @@
         <v>79</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>79</v>
@@ -5863,11 +5771,11 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>320</v>
+        <v>254</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
@@ -5885,7 +5793,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>321</v>
+        <v>250</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5903,61 +5811,61 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>79</v>
+        <v>255</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>256</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>134</v>
+        <v>257</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>260</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -5981,13 +5889,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6005,45 +5913,45 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>79</v>
+        <v>268</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>79</v>
+        <v>271</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6054,27 +5962,29 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>281</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6099,13 +6009,11 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6123,77 +6031,79 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>326</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6229,46 +6139,46 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="AC38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AD38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AF38" t="s" s="2">
+      <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AN38" t="s" s="2">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6276,10 +6186,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>327</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6287,7 +6197,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>91</v>
@@ -6299,19 +6209,19 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>105</v>
+        <v>294</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6319,7 +6229,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>79</v>
@@ -6361,10 +6271,10 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>91</v>
@@ -6373,22 +6283,22 @@
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>134</v>
+        <v>300</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6396,10 +6306,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6407,30 +6317,32 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>158</v>
+        <v>303</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6467,19 +6379,17 @@
         <v>79</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6494,19 +6404,19 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>134</v>
+        <v>310</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -6514,20 +6424,20 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
@@ -6539,18 +6449,20 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>314</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -6599,34 +6511,34 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -6634,10 +6546,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6651,7 +6563,7 @@
         <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>79</v>
@@ -6660,15 +6572,17 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6705,19 +6619,17 @@
         <v>79</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6726,10 +6638,10 @@
         <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -6741,23 +6653,25 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>79</v>
       </c>
@@ -6766,10 +6680,10 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>79</v>
@@ -6778,15 +6692,17 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>137</v>
+        <v>314</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6823,31 +6739,31 @@
         <v>79</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>79</v>
+        <v>320</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -6859,10 +6775,10 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>321</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -6870,10 +6786,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6881,7 +6797,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -6893,27 +6809,25 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>105</v>
+        <v>314</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>330</v>
+        <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>79</v>
@@ -6955,10 +6869,10 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>91</v>
@@ -6967,7 +6881,7 @@
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
@@ -6976,13 +6890,13 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>134</v>
+        <v>330</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -6990,10 +6904,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7013,16 +6927,16 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7073,7 +6987,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7097,10 +7011,10 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>134</v>
+        <v>336</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7108,10 +7022,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7119,7 +7033,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>91</v>
@@ -7131,72 +7045,70 @@
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>105</v>
+        <v>333</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>311</v>
+        <v>339</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="S46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="AG46" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>91</v>
@@ -7205,7 +7117,7 @@
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
@@ -7214,13 +7126,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>134</v>
+        <v>342</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -7228,10 +7140,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7242,7 +7154,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7254,13 +7166,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7311,19 +7223,19 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>348</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7335,7 +7247,7 @@
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>134</v>
+        <v>349</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7346,10 +7258,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7369,20 +7281,18 @@
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>281</v>
+        <v>151</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>343</v>
+        <v>152</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7431,7 +7341,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>346</v>
+        <v>154</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7440,10 +7350,10 @@
         <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -7455,7 +7365,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7466,21 +7376,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -7489,19 +7399,19 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>351</v>
+        <v>206</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7527,13 +7437,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>353</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7551,19 +7461,19 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>354</v>
+        <v>160</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -7575,7 +7485,7 @@
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7586,33 +7496,33 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>356</v>
@@ -7621,9 +7531,11 @@
         <v>357</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
@@ -7671,45 +7583,45 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AG50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="B51" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7723,26 +7635,24 @@
         <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>281</v>
+        <v>188</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7767,13 +7677,11 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>79</v>
+        <v>362</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -7791,7 +7699,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7800,7 +7708,7 @@
         <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>103</v>
@@ -7809,13 +7717,13 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>134</v>
+        <v>271</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7826,10 +7734,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7840,7 +7748,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7849,10 +7757,10 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>275</v>
+        <v>366</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>367</v>
@@ -7909,16 +7817,16 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>103</v>
@@ -7930,13 +7838,13 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN52" t="s" s="2">
-        <v>370</v>
-      </c>
       <c r="AO52" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>79</v>
@@ -7944,10 +7852,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7958,7 +7866,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -7970,13 +7878,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>373</v>
+        <v>188</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8003,13 +7911,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8027,19 +7935,19 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>376</v>
+        <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8051,7 +7959,7 @@
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8062,10 +7970,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8076,7 +7984,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -8088,15 +7996,17 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>281</v>
+        <v>345</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>282</v>
+        <v>377</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8145,19 +8055,19 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>284</v>
+        <v>376</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>79</v>
+        <v>380</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8169,7 +8079,7 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>285</v>
+        <v>381</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8180,21 +8090,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8206,17 +8116,15 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8265,19 +8173,19 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>290</v>
+        <v>154</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
@@ -8289,7 +8197,7 @@
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>285</v>
+        <v>155</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8300,14 +8208,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>381</v>
+        <v>203</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8320,26 +8228,24 @@
         <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8387,7 +8293,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>384</v>
+        <v>160</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8411,7 +8317,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8420,44 +8326,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I57" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I57" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="J57" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
       </c>
@@ -8481,11 +8391,13 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
@@ -8503,31 +8415,31 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>385</v>
+        <v>358</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>389</v>
+        <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>212</v>
+        <v>134</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8538,10 +8450,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8561,16 +8473,16 @@
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>392</v>
+        <v>188</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8597,13 +8509,13 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>79</v>
+        <v>265</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>79</v>
+        <v>388</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -8621,7 +8533,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8630,25 +8542,25 @@
         <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>79</v>
@@ -8656,10 +8568,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8670,7 +8582,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -8679,16 +8591,16 @@
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>158</v>
+        <v>395</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8715,13 +8627,13 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>399</v>
+        <v>79</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>79</v>
@@ -8739,16 +8651,16 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>103</v>
@@ -8763,21 +8675,21 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>401</v>
+        <v>369</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8788,10 +8700,10 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>79</v>
@@ -8800,17 +8712,15 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -8859,7 +8769,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8871,743 +8781,29 @@
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>406</v>
+        <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP66" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP66">
+  <autoFilter ref="A1:AP60">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9617,7 +8813,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/main/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
